--- a/artfynd/S 4001-2024 artfynd.xlsx
+++ b/artfynd/S 4001-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379672</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379678</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934775</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718971</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54818461</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379740</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119495543</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718974</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1568,6 +1613,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934786</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,6 +1719,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934792</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54818460</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1868,6 +1928,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61126641</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1965,6 +2030,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379677</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2062,6 +2132,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379681</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2159,6 +2234,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718987</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2260,6 +2340,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934823</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2357,6 +2442,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16580293</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2454,6 +2544,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61126642</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2551,6 +2646,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379674</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2648,6 +2748,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379676</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2745,6 +2850,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379734</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2842,6 +2952,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379735</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2939,6 +3054,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379738</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3036,6 +3156,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379673</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3138,6 +3263,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224524</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3240,6 +3370,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224526</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3342,6 +3477,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224527</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3444,6 +3584,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224529</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3541,6 +3686,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379737</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3638,6 +3788,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379739</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3744,6 +3899,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313635</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3858,6 +4018,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313653</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3955,6 +4120,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379675</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4052,6 +4222,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379679</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4149,6 +4324,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379682</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4246,6 +4426,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379683</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4343,6 +4528,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379733</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4449,6 +4639,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313697</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4546,6 +4741,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718982</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4647,6 +4847,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934808</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4744,6 +4949,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718955</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4846,6 +5056,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934752</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4943,8 +5158,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934753</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>